--- a/output/graficos_envejecimiento/plot_comunal_d_enveje_a_2024_araucania.xlsx
+++ b/output/graficos_envejecimiento/plot_comunal_d_enveje_a_2024_araucania.xlsx
@@ -416,7 +416,7 @@
         <v>59.22797223344475</v>
       </c>
       <c r="E3">
-        <v>24.24431630366915</v>
+        <v>24.24431630366916</v>
       </c>
     </row>
     <row r="4">
@@ -454,7 +454,7 @@
         <v>60.02532714225411</v>
       </c>
       <c r="E5">
-        <v>21.43309413254538</v>
+        <v>21.43309413254537</v>
       </c>
     </row>
     <row r="6">
@@ -546,7 +546,7 @@
         <v>16.11048844860624</v>
       </c>
       <c r="D10">
-        <v>58.92837774323005</v>
+        <v>58.92837774323006</v>
       </c>
       <c r="E10">
         <v>24.96113380816371</v>
@@ -603,7 +603,7 @@
         <v>18.23624576361253</v>
       </c>
       <c r="D13">
-        <v>62.62886293589032</v>
+        <v>62.62886293589033</v>
       </c>
       <c r="E13">
         <v>19.13489130049715</v>
@@ -622,7 +622,7 @@
         <v>17.23881521873838</v>
       </c>
       <c r="D14">
-        <v>59.99504275622754</v>
+        <v>59.99504275622753</v>
       </c>
       <c r="E14">
         <v>22.76614202503408</v>
@@ -641,7 +641,7 @@
         <v>16.31170216311702</v>
       </c>
       <c r="D15">
-        <v>59.4707195947072</v>
+        <v>59.47071959470719</v>
       </c>
       <c r="E15">
         <v>24.21757824217578</v>
@@ -774,7 +774,7 @@
         <v>19.17985807860262</v>
       </c>
       <c r="D22">
-        <v>59.94132096069869</v>
+        <v>59.94132096069868</v>
       </c>
       <c r="E22">
         <v>20.87882096069869</v>
@@ -831,7 +831,7 @@
         <v>16.03643126221926</v>
       </c>
       <c r="D25">
-        <v>57.10266558580897</v>
+        <v>57.10266558580898</v>
       </c>
       <c r="E25">
         <v>26.86090315197177</v>
@@ -866,10 +866,10 @@
         <v>110.8474576271186</v>
       </c>
       <c r="C27">
-        <v>18.98326898326898</v>
+        <v>18.98326898326899</v>
       </c>
       <c r="D27">
-        <v>59.97425997425997</v>
+        <v>59.97425997425998</v>
       </c>
       <c r="E27">
         <v>21.04247104247104</v>
@@ -891,7 +891,7 @@
         <v>58.44971172325432</v>
       </c>
       <c r="E28">
-        <v>24.76617552850737</v>
+        <v>24.76617552850736</v>
       </c>
     </row>
     <row r="29">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="B30">
-        <v>142.3504273504273</v>
+        <v>142.3504273504274</v>
       </c>
       <c r="C30">
         <v>16.61577788823404</v>
@@ -942,10 +942,10 @@
         <v>127.6070763500931</v>
       </c>
       <c r="C31">
-        <v>16.82199075886914</v>
+        <v>16.82199075886913</v>
       </c>
       <c r="D31">
-        <v>61.71195864985512</v>
+        <v>61.71195864985511</v>
       </c>
       <c r="E31">
         <v>21.46605059127575</v>
@@ -964,7 +964,7 @@
         <v>17.26734548898887</v>
       </c>
       <c r="D32">
-        <v>56.75112479280133</v>
+        <v>56.75112479280132</v>
       </c>
       <c r="E32">
         <v>25.9815297182098</v>
@@ -983,7 +983,7 @@
         <v>16.90096267967823</v>
       </c>
       <c r="D33">
-        <v>58.80258472899908</v>
+        <v>58.80258472899907</v>
       </c>
       <c r="E33">
         <v>24.29645259132269</v>
